--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0141.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0141.xlsx
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Ta sẽ giải mã mấy cái mã này, rồi chúng ta có thể... Ồ, xin lỗi...</t>
+          <t>Tao sẽ giải mã mấy cái mã này, rồi chúng ta có thể... Ồ, xin lỗi...</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Khóa phòng thí nghiệm lại. Ta đang tới. Nhật ký thí nghiệm thì sao?</t>
+          <t>Khóa phòng thí nghiệm lại. Tao đang tới. Nhật ký thí nghiệm thì sao?</t>
         </is>
       </c>
     </row>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Hello?</t>
+          <t>Xin chào?</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Ta không hiểu lắm...</t>
+          <t>Tao không hiểu lắm...</t>
         </is>
       </c>
     </row>
@@ -9934,7 +9934,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Sao cậu biết?</t>
+          <t>Sao cậu biết được?</t>
         </is>
       </c>
     </row>
@@ -12144,7 +12144,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Ừ. Á! Ta đòi lại tiền đây!</t>
+          <t>Ừ. Á! Tao đòi lại tiền đây!</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Ta biết {PlayerName} làm được mà.</t>
+          <t>Tao biết {PlayerName} làm được mà.</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Chuyện gì đang xảy ra vậy?</t>
+          <t>Có chuyện gì vậy?</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Haha. Một cảnh tượng giống như trong vở kịch anh hùng mà bọn trẻ con thích xem... nếu ta nhớ không lầm.</t>
+          <t>Haha. Một cảnh tượng giống như trong vở kịch anh hùng mà bọn trẻ con thích xem... nếu tao nhớ không lầm.</t>
         </is>
       </c>
     </row>
@@ -15849,7 +15849,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Ta chưa từng đến thăm hắn một lần nào trong những đợt kiểm tra cuối, mà lại là người duy nhất còn lại trong dự án. Thất bại là điều không tránh khỏi.</t>
+          <t>Tao chưa từng đến thăm hắn một lần nào trong những đợt kiểm tra cuối, mà lại là người duy nhất còn lại trong dự án. Thất bại là điều không tránh khỏi.</t>
         </is>
       </c>
     </row>
@@ -16434,7 +16434,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Okay..</t>
+          <t>Ừm...</t>
         </is>
       </c>
     </row>
@@ -21764,7 +21764,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Hê hê, sao mấy đứa trẻ lại để bà già như ta bỏ xa thế? Nhanh lên nào, bà đang đợi đấy!</t>
+          <t>Hê hê, sao mấy đứa trẻ lại để bà già như tao bỏ xa thế? Nhanh lên nào, bà đang đợi đấy!</t>
         </is>
       </c>
     </row>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Phần thưởng à? Tính ta vào!</t>
+          <t>Phần thưởng à? Tính tao vào!</t>
         </is>
       </c>
     </row>
@@ -23909,7 +23909,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Ta nghe nói cậu là người đã dạy hắn vượt qua nỗi sợ nước...</t>
+          <t>Tao nghe nói cậu là người đã dạy hắn vượt qua nỗi sợ nước...</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>...Tch. Ta sẽ méc Mahn nếu ngươi còn làm thế. Đợi hắn về, cho ngươi ăn đấm bây giờ.</t>
+          <t>...Tch. Tao sẽ méc Mahn nếu mày còn làm thế. Đợi hắn về, cho mày ăn đấm bây giờ.</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Pfft, cậu nghĩ mách Mahn là xong à? Có hắn ở đó, cậu đừng hòng trở thành Flame Ranger!</t>
+          <t>Pfft, mày nghĩ mách Mahn là xong à? Có hắn ở đó, mày đừng hòng trở thành Flame Ranger!</t>
         </is>
       </c>
     </row>
@@ -25859,7 +25859,7 @@
       </c>
       <c r="M391" t="inlineStr">
         <is>
-          <t>Ít nhất ta sẽ không bị ngươi đánh liên tục nữa!</t>
+          <t>Ít nhất tao sẽ không bị mày đánh liên tục nữa!</t>
         </is>
       </c>
     </row>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Mahn không có ở đây đâu, giờ ta phụ trách! Muốn chơi với tụi ta không? Được rồi, vậy ngươi làm quái vật nhé!</t>
+          <t>Mahn không có ở đây đâu, giờ tao phụ trách! Muốn chơi với tụi tao không? Được rồi, vậy mày làm quái vật nhé!</t>
         </is>
       </c>
     </row>
@@ -28589,7 +28589,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Ừm... Cảm ơn {Male=anh;Female=chị} đã cứu con, {Male=anh;Female=chị} ơi.</t>
+          <t>Ừm... Cảm ơn bạn đã cứu con, {Male=mister;Female=miss} ơi.</t>
         </is>
       </c>
     </row>
@@ -32099,7 +32099,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Ta sẽ thử.</t>
+          <t>Tao sẽ thử.</t>
         </is>
       </c>
     </row>
